--- a/Paper1/data/Table3_hotspots.xlsx
+++ b/Paper1/data/Table3_hotspots.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,82 +436,23 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PM2.5 (ug/m3)</t>
+          <t>Subdistrict / District</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Gi* z-score</t>
+          <t>PM2.5 (ug/m3)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Gi* z-score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>p-value</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>จุดตรวจวัดอากาศ-12</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3.161659054848977</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.007000000216066837</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>จุดตรวจวัดอากาศ-survey-1</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>21.51</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.085120362554359</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.004000000189989805</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>จุดตรวจวัดอากาศ-survey-0</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.642080364669898</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.008999999612569809</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>จุดตรวจวัดอากาศ-survey-2</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.251105235032034</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0430000014603138</v>
       </c>
     </row>
   </sheetData>
